--- a/05-data/source-data.xlsx
+++ b/05-data/source-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://prodduke-my.sharepoint.com/personal/jr555_duke_edu/Documents/research/hydrology/repo/05-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="178" documentId="8_{72C342FF-24D5-464C-A1D9-A195B6C12920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C0E004E-4AA7-C844-8B12-BC3A65B498C5}"/>
+  <xr:revisionPtr revIDLastSave="189" documentId="8_{72C342FF-24D5-464C-A1D9-A195B6C12920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDC07A5C-05F7-2641-BB49-C3AE916B50CE}"/>
   <bookViews>
-    <workbookView xWindow="3580" yWindow="1180" windowWidth="28040" windowHeight="17440" activeTab="9" xr2:uid="{73057207-5C9D-564F-85EB-109BBE658AC7}"/>
+    <workbookView xWindow="1360" yWindow="740" windowWidth="28040" windowHeight="16720" activeTab="9" xr2:uid="{73057207-5C9D-564F-85EB-109BBE658AC7}"/>
   </bookViews>
   <sheets>
     <sheet name="Fig. 1a" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="59">
   <si>
     <t>distance</t>
   </si>
@@ -217,6 +217,12 @@
   <si>
     <t>zhang_2018</t>
   </si>
+  <si>
+    <t>window21</t>
+  </si>
+  <si>
+    <t>min_2019</t>
+  </si>
 </sst>
 </file>
 
@@ -275,6 +281,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10525,18 +10535,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00CB6234-721C-AA4E-BC97-D7F51586B9CA}">
-  <dimension ref="A1:U39"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -10600,8 +10610,11 @@
       <c r="U2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>0</v>
       </c>
@@ -10621,52 +10634,55 @@
         <v>2.1346012664601701E-2</v>
       </c>
       <c r="G3">
-        <v>2.4475344299258499E-2</v>
+        <v>2.34048714883375E-2</v>
       </c>
       <c r="H3">
-        <v>2.75644291266617E-2</v>
+        <v>2.68858371040093E-2</v>
       </c>
       <c r="I3">
-        <v>3.1355100354250501E-2</v>
+        <v>2.9542149866884099E-2</v>
       </c>
       <c r="J3">
-        <v>3.5792401045611003E-2</v>
+        <v>3.4578067505877601E-2</v>
       </c>
       <c r="K3">
-        <v>3.9767706077978297E-2</v>
+        <v>3.8759296241476601E-2</v>
       </c>
       <c r="L3">
-        <v>4.30407361788629E-2</v>
+        <v>4.2310217574556802E-2</v>
       </c>
       <c r="M3">
-        <v>4.5803332305675702E-2</v>
+        <v>4.5147201096196403E-2</v>
       </c>
       <c r="N3">
-        <v>4.8547151277902698E-2</v>
+        <v>4.7785379945679801E-2</v>
       </c>
       <c r="O3">
-        <v>5.1055012234725798E-2</v>
+        <v>5.0303104623276897E-2</v>
       </c>
       <c r="P3">
-        <v>5.3547714877308999E-2</v>
+        <v>5.2641111571446797E-2</v>
       </c>
       <c r="Q3">
-        <v>5.7674157569962699E-2</v>
+        <v>5.5041125436196103E-2</v>
       </c>
       <c r="R3">
-        <v>6.2803543304918094E-2</v>
+        <v>5.99937415275823E-2</v>
       </c>
       <c r="S3">
-        <v>6.7651718544938996E-2</v>
+        <v>6.47645514579957E-2</v>
       </c>
       <c r="T3">
-        <v>7.2693459708964306E-2</v>
+        <v>6.9264038973357894E-2</v>
       </c>
       <c r="U3">
-        <v>7.7906443617215701E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+        <v>7.4218935209661996E-2</v>
+      </c>
+      <c r="V3">
+        <v>7.9821187258198895E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>200</v>
       </c>
@@ -10686,52 +10702,55 @@
         <v>2.2073642944084499E-2</v>
       </c>
       <c r="G4">
-        <v>2.5199005571421299E-2</v>
+        <v>2.4125713346646802E-2</v>
       </c>
       <c r="H4">
-        <v>2.8206144217813998E-2</v>
+        <v>2.7439737971582199E-2</v>
       </c>
       <c r="I4">
-        <v>3.2181083196079298E-2</v>
+        <v>3.00144056347393E-2</v>
       </c>
       <c r="J4">
-        <v>3.6423210672196497E-2</v>
+        <v>3.4979620675464701E-2</v>
       </c>
       <c r="K4">
-        <v>4.0080632827098797E-2</v>
+        <v>3.8786624592027301E-2</v>
       </c>
       <c r="L4">
-        <v>4.35198208259652E-2</v>
+        <v>4.24699284463061E-2</v>
       </c>
       <c r="M4">
-        <v>4.6853814990507503E-2</v>
+        <v>4.5791067816403401E-2</v>
       </c>
       <c r="N4">
-        <v>5.0058704030533897E-2</v>
+        <v>4.8905010491830402E-2</v>
       </c>
       <c r="O4">
-        <v>5.3226913977404498E-2</v>
+        <v>5.1951400840546898E-2</v>
       </c>
       <c r="P4">
-        <v>5.6225412514439903E-2</v>
+        <v>5.4865616748799598E-2</v>
       </c>
       <c r="Q4">
-        <v>6.1137032502288198E-2</v>
+        <v>5.7672998021587103E-2</v>
       </c>
       <c r="R4">
-        <v>6.7416868205948596E-2</v>
+        <v>6.3323903858768807E-2</v>
       </c>
       <c r="S4">
-        <v>7.3890259339828901E-2</v>
+        <v>6.9294032817166007E-2</v>
       </c>
       <c r="T4">
-        <v>8.0527384595058094E-2</v>
+        <v>7.5702731672329701E-2</v>
       </c>
       <c r="U4">
-        <v>8.7404367620276202E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+        <v>8.2383086575501405E-2</v>
+      </c>
+      <c r="V4">
+        <v>8.9319106161668299E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>400</v>
       </c>
@@ -10751,52 +10770,55 @@
         <v>2.44349157879356E-2</v>
       </c>
       <c r="G5">
-        <v>2.87045625409631E-2</v>
+        <v>2.7192642169031001E-2</v>
       </c>
       <c r="H5">
-        <v>3.3165040357032001E-2</v>
+        <v>3.2018921634799899E-2</v>
       </c>
       <c r="I5">
-        <v>3.9461017980024202E-2</v>
+        <v>3.60210896051932E-2</v>
       </c>
       <c r="J5">
-        <v>4.5819037611584498E-2</v>
+        <v>4.3530068446643297E-2</v>
       </c>
       <c r="K5">
-        <v>5.0642182126155601E-2</v>
+        <v>4.9062533224942702E-2</v>
       </c>
       <c r="L5">
-        <v>5.45172975436191E-2</v>
+        <v>5.3155245978682701E-2</v>
       </c>
       <c r="M5">
-        <v>5.7908168047360403E-2</v>
+        <v>5.6518226160310603E-2</v>
       </c>
       <c r="N5">
-        <v>6.11489319569384E-2</v>
+        <v>5.9670163908826103E-2</v>
       </c>
       <c r="O5">
-        <v>6.4460506365556294E-2</v>
+        <v>6.2867665491667196E-2</v>
       </c>
       <c r="P5">
-        <v>6.7974255922410604E-2</v>
+        <v>6.6249905489894595E-2</v>
       </c>
       <c r="Q5">
-        <v>7.3842697831214499E-2</v>
+        <v>6.9693628871844895E-2</v>
       </c>
       <c r="R5">
-        <v>8.0700579947258502E-2</v>
+        <v>7.6521267665342202E-2</v>
       </c>
       <c r="S5">
-        <v>8.7272867294274997E-2</v>
+        <v>8.3225044990549404E-2</v>
       </c>
       <c r="T5">
-        <v>9.3327893008312596E-2</v>
+        <v>8.9399033042297293E-2</v>
       </c>
       <c r="U5">
-        <v>9.8740178297581305E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+        <v>9.5097444321513597E-2</v>
+      </c>
+      <c r="V5">
+        <v>0.10022706779523601</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>600</v>
       </c>
@@ -10816,52 +10838,55 @@
         <v>2.4459417070685899E-2</v>
       </c>
       <c r="G6">
-        <v>2.8844945496815901E-2</v>
+        <v>2.7193674203978401E-2</v>
       </c>
       <c r="H6">
-        <v>3.3781904731579299E-2</v>
+        <v>3.22360644984531E-2</v>
       </c>
       <c r="I6">
-        <v>4.24098660243259E-2</v>
+        <v>3.6944401254777E-2</v>
       </c>
       <c r="J6">
-        <v>5.08286396293555E-2</v>
+        <v>4.69051187504127E-2</v>
       </c>
       <c r="K6">
-        <v>5.7498388994314198E-2</v>
+        <v>5.4624075624245802E-2</v>
       </c>
       <c r="L6">
-        <v>6.2727498339560803E-2</v>
+        <v>6.0663642248867902E-2</v>
       </c>
       <c r="M6">
-        <v>6.7236507876115695E-2</v>
+        <v>6.5529848084843995E-2</v>
       </c>
       <c r="N6">
-        <v>7.1301897318396798E-2</v>
+        <v>6.9673631979612002E-2</v>
       </c>
       <c r="O6">
-        <v>7.5036556750013098E-2</v>
+        <v>7.3383957150333204E-2</v>
       </c>
       <c r="P6">
-        <v>7.8593436454077306E-2</v>
+        <v>7.6946706664703005E-2</v>
       </c>
       <c r="Q6">
-        <v>8.3766435437184206E-2</v>
+        <v>8.0349521744829705E-2</v>
       </c>
       <c r="R6">
-        <v>8.9990391914174794E-2</v>
+        <v>8.6601401187559102E-2</v>
       </c>
       <c r="S6">
-        <v>9.5560656210407602E-2</v>
+        <v>9.2256935404423299E-2</v>
       </c>
       <c r="T6">
-        <v>0.100268412262753</v>
+        <v>9.7190741676903503E-2</v>
       </c>
       <c r="U6">
-        <v>0.104266998852592</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+        <v>0.101410950287464</v>
+      </c>
+      <c r="V6">
+        <v>0.104996496141652</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>800</v>
       </c>
@@ -10881,52 +10906,55 @@
         <v>2.2668692022929999E-2</v>
       </c>
       <c r="G7">
-        <v>2.6729688055464801E-2</v>
+        <v>2.53358132080897E-2</v>
       </c>
       <c r="H7">
-        <v>3.1517567186861703E-2</v>
+        <v>3.0156335629028402E-2</v>
       </c>
       <c r="I7">
-        <v>4.0291190336680098E-2</v>
+        <v>3.4833173844606199E-2</v>
       </c>
       <c r="J7">
-        <v>5.0707346789888301E-2</v>
+        <v>4.5934050072531298E-2</v>
       </c>
       <c r="K7">
-        <v>5.9504201649842603E-2</v>
+        <v>5.5610169905853803E-2</v>
       </c>
       <c r="L7">
-        <v>6.6994524967213101E-2</v>
+        <v>6.3695057897788995E-2</v>
       </c>
       <c r="M7">
-        <v>7.3278999750569201E-2</v>
+        <v>7.0561275311095295E-2</v>
       </c>
       <c r="N7">
-        <v>7.8481099572447005E-2</v>
+        <v>7.6156201725765593E-2</v>
       </c>
       <c r="O7">
-        <v>8.2823048538403096E-2</v>
+        <v>8.0797490757438306E-2</v>
       </c>
       <c r="P7">
-        <v>8.6515795337639798E-2</v>
+        <v>8.4722028219997594E-2</v>
       </c>
       <c r="Q7">
-        <v>9.1929675980736994E-2</v>
+        <v>8.8174982917504904E-2</v>
       </c>
       <c r="R7">
-        <v>9.7683006030660102E-2</v>
+        <v>9.4303891585420699E-2</v>
       </c>
       <c r="S7">
-        <v>0.10240501137809301</v>
+        <v>9.9421347448673897E-2</v>
       </c>
       <c r="T7">
-        <v>0.106089222205314</v>
+        <v>0.10355755828579701</v>
       </c>
       <c r="U7">
-        <v>0.108943134998728</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+        <v>0.106830636104642</v>
+      </c>
+      <c r="V7">
+        <v>0.10937250020801199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1000</v>
       </c>
@@ -10946,52 +10974,55 @@
         <v>1.19316030889959E-2</v>
       </c>
       <c r="G8">
-        <v>1.4189918261520801E-2</v>
+        <v>1.33400425282453E-2</v>
       </c>
       <c r="H8">
-        <v>1.6966591416223201E-2</v>
+        <v>1.612976343677E-2</v>
       </c>
       <c r="I8">
-        <v>2.2586037692682501E-2</v>
+        <v>1.8969468319816302E-2</v>
       </c>
       <c r="J8">
-        <v>2.97604559989951E-2</v>
+        <v>2.62928810950676E-2</v>
       </c>
       <c r="K8">
-        <v>3.6766338152792503E-2</v>
+        <v>3.3536484844474398E-2</v>
       </c>
       <c r="L8">
-        <v>4.3101170601859501E-2</v>
+        <v>4.0321911671384499E-2</v>
       </c>
       <c r="M8">
-        <v>4.8780670823841701E-2</v>
+        <v>4.6294510556021497E-2</v>
       </c>
       <c r="N8">
-        <v>5.39063214214065E-2</v>
+        <v>5.1685908331642397E-2</v>
       </c>
       <c r="O8">
-        <v>5.8506942136100901E-2</v>
+        <v>5.6524642875005603E-2</v>
       </c>
       <c r="P8">
-        <v>6.2678499265758303E-2</v>
+        <v>6.0815093005941102E-2</v>
       </c>
       <c r="Q8">
-        <v>6.8651465304369705E-2</v>
+        <v>6.4665918845019404E-2</v>
       </c>
       <c r="R8">
-        <v>7.4950780579203596E-2</v>
+        <v>7.1470740133675895E-2</v>
       </c>
       <c r="S8">
-        <v>8.0254992452047799E-2</v>
+        <v>7.7161013647108298E-2</v>
       </c>
       <c r="T8">
-        <v>8.4873370634865497E-2</v>
+        <v>8.2031726226551999E-2</v>
       </c>
       <c r="U8">
-        <v>8.8807920203856403E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+        <v>8.6101754637828307E-2</v>
+      </c>
+      <c r="V8">
+        <v>8.96670045848042E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1200</v>
       </c>
@@ -11011,52 +11042,55 @@
         <v>9.1749495260930493E-3</v>
       </c>
       <c r="G9">
-        <v>1.0709059355983199E-2</v>
+        <v>1.01868970033602E-2</v>
       </c>
       <c r="H9">
-        <v>1.2682761796839999E-2</v>
+        <v>1.2210317750956001E-2</v>
       </c>
       <c r="I9">
-        <v>1.5897829879412802E-2</v>
+        <v>1.41109783818594E-2</v>
       </c>
       <c r="J9">
-        <v>2.05594425831136E-2</v>
+        <v>1.8827239267284301E-2</v>
       </c>
       <c r="K9">
-        <v>2.55348823244467E-2</v>
+        <v>2.36693805002334E-2</v>
       </c>
       <c r="L9">
-        <v>3.0912165629578599E-2</v>
+        <v>2.8899766742726402E-2</v>
       </c>
       <c r="M9">
-        <v>3.6344945384528503E-2</v>
+        <v>3.4395272024529099E-2</v>
       </c>
       <c r="N9">
-        <v>4.1546633103242699E-2</v>
+        <v>3.9721577443169197E-2</v>
       </c>
       <c r="O9">
-        <v>4.6327485227726603E-2</v>
+        <v>4.4719718955535802E-2</v>
       </c>
       <c r="P9">
-        <v>5.0806001722782601E-2</v>
+        <v>4.9366218636041001E-2</v>
       </c>
       <c r="Q9">
-        <v>5.6609533361579902E-2</v>
+        <v>5.3689286702787997E-2</v>
       </c>
       <c r="R9">
-        <v>6.4164686054908396E-2</v>
+        <v>6.1801181068233998E-2</v>
       </c>
       <c r="S9">
-        <v>7.0753175113462602E-2</v>
+        <v>6.8988660571927901E-2</v>
       </c>
       <c r="T9">
-        <v>7.6168150513762398E-2</v>
+        <v>7.4976452817029901E-2</v>
       </c>
       <c r="U9">
-        <v>8.0614130240512297E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+        <v>7.9830807966322595E-2</v>
+      </c>
+      <c r="V9">
+        <v>8.3747291071258001E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1400</v>
       </c>
@@ -11076,52 +11110,55 @@
         <v>7.1142622907583103E-3</v>
       </c>
       <c r="G10">
-        <v>8.2079104350798304E-3</v>
+        <v>7.8433189169729509E-3</v>
       </c>
       <c r="H10">
-        <v>9.5467159908277192E-3</v>
+        <v>9.2132333459803602E-3</v>
       </c>
       <c r="I10">
-        <v>1.17433007574401E-2</v>
+        <v>1.0528374549329599E-2</v>
       </c>
       <c r="J10">
-        <v>1.4819806775946E-2</v>
+        <v>1.3657526953498899E-2</v>
       </c>
       <c r="K10">
-        <v>1.7908284892416099E-2</v>
+        <v>1.6736764972532299E-2</v>
       </c>
       <c r="L10">
-        <v>2.11542653715752E-2</v>
+        <v>1.9955838668905899E-2</v>
       </c>
       <c r="M10">
-        <v>2.4569119680815901E-2</v>
+        <v>2.3349226460475499E-2</v>
       </c>
       <c r="N10">
-        <v>2.8148125810818301E-2</v>
+        <v>2.6888603619492999E-2</v>
       </c>
       <c r="O10">
-        <v>3.1875616415077801E-2</v>
+        <v>3.0614538887346301E-2</v>
       </c>
       <c r="P10">
-        <v>3.5631257968368302E-2</v>
+        <v>3.43711055815418E-2</v>
       </c>
       <c r="Q10">
-        <v>4.0989315225340203E-2</v>
+        <v>3.81483887202256E-2</v>
       </c>
       <c r="R10">
-        <v>4.8087549450977297E-2</v>
+        <v>4.5524720754138902E-2</v>
       </c>
       <c r="S10">
-        <v>5.4648588240554602E-2</v>
+        <v>5.2527680147547197E-2</v>
       </c>
       <c r="T10">
-        <v>6.0719381622206997E-2</v>
+        <v>5.8995656278541302E-2</v>
       </c>
       <c r="U10">
-        <v>6.63373066802736E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+        <v>6.4930341693792304E-2</v>
+      </c>
+      <c r="V10">
+        <v>7.0315458246589205E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1600</v>
       </c>
@@ -11141,52 +11178,55 @@
         <v>5.5453632282120397E-3</v>
       </c>
       <c r="G11">
-        <v>6.2652202025777204E-3</v>
+        <v>6.0125133521787104E-3</v>
       </c>
       <c r="H11">
-        <v>7.0799320279554701E-3</v>
+        <v>6.8675526437520099E-3</v>
       </c>
       <c r="I11">
-        <v>8.4696936398718902E-3</v>
+        <v>7.6998342818882402E-3</v>
       </c>
       <c r="J11">
-        <v>1.0282882075414701E-2</v>
+        <v>9.5666675796788302E-3</v>
       </c>
       <c r="K11">
-        <v>1.2062243630480699E-2</v>
+        <v>1.1316043735844701E-2</v>
       </c>
       <c r="L11">
-        <v>1.39032522096336E-2</v>
+        <v>1.30902019167398E-2</v>
       </c>
       <c r="M11">
-        <v>1.5755215601600699E-2</v>
+        <v>1.4972107029150699E-2</v>
       </c>
       <c r="N11">
-        <v>1.7719653888272499E-2</v>
+        <v>1.69110232105909E-2</v>
       </c>
       <c r="O11">
-        <v>1.9793923883013199E-2</v>
+        <v>1.8996973350406201E-2</v>
       </c>
       <c r="P11">
-        <v>2.1997098094436E-2</v>
+        <v>2.1191411662337099E-2</v>
       </c>
       <c r="Q11">
-        <v>2.5491186258552199E-2</v>
+        <v>2.3506833963147799E-2</v>
       </c>
       <c r="R11">
-        <v>3.07138942750033E-2</v>
+        <v>2.85730348043613E-2</v>
       </c>
       <c r="S11">
-        <v>3.6133250302442702E-2</v>
+        <v>3.4025004424104298E-2</v>
       </c>
       <c r="T11">
-        <v>4.1470435915220601E-2</v>
+        <v>3.9533034007895797E-2</v>
       </c>
       <c r="U11">
-        <v>4.6663300111284799E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+        <v>4.4951442107013101E-2</v>
+      </c>
+      <c r="V11">
+        <v>5.0206217914791899E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1800</v>
       </c>
@@ -11206,52 +11246,55 @@
         <v>4.7591878727754802E-3</v>
       </c>
       <c r="G12">
-        <v>5.3514927857596104E-3</v>
+        <v>5.1468331156533896E-3</v>
       </c>
       <c r="H12">
-        <v>6.0291348322741396E-3</v>
+        <v>5.8466585266635099E-3</v>
       </c>
       <c r="I12">
-        <v>7.1651558585520397E-3</v>
+        <v>6.4459165576891903E-3</v>
       </c>
       <c r="J12">
-        <v>8.4849664996835706E-3</v>
+        <v>7.8344457200383993E-3</v>
       </c>
       <c r="K12">
-        <v>9.7820176286243406E-3</v>
+        <v>9.1694107277676008E-3</v>
       </c>
       <c r="L12">
-        <v>1.10303398379568E-2</v>
+        <v>1.0458663381069801E-2</v>
       </c>
       <c r="M12">
-        <v>1.2284383573435699E-2</v>
+        <v>1.1718922869238001E-2</v>
       </c>
       <c r="N12">
-        <v>1.35281250392795E-2</v>
+        <v>1.29661228171137E-2</v>
       </c>
       <c r="O12">
-        <v>1.4788087697710501E-2</v>
+        <v>1.42283006203761E-2</v>
       </c>
       <c r="P12">
-        <v>1.6060137178539199E-2</v>
+        <v>1.5503692762223501E-2</v>
       </c>
       <c r="Q12">
-        <v>1.8156041281045601E-2</v>
+        <v>1.68057686237944E-2</v>
       </c>
       <c r="R12">
-        <v>2.0883351714895301E-2</v>
+        <v>1.9566997241355199E-2</v>
       </c>
       <c r="S12">
-        <v>2.3643652254361901E-2</v>
+        <v>2.23818282232939E-2</v>
       </c>
       <c r="T12">
-        <v>2.6478289386616099E-2</v>
+        <v>2.52847156378764E-2</v>
       </c>
       <c r="U12">
-        <v>2.94607959609961E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+        <v>2.8291550503466399E-2</v>
+      </c>
+      <c r="V12">
+        <v>3.14726332038337E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2000</v>
       </c>
@@ -11271,52 +11314,55 @@
         <v>4.9339731394936297E-3</v>
       </c>
       <c r="G13">
-        <v>5.37706287436252E-3</v>
+        <v>5.2379395900898698E-3</v>
       </c>
       <c r="H13">
-        <v>5.86659706997296E-3</v>
+        <v>5.7680492286650798E-3</v>
       </c>
       <c r="I13">
-        <v>6.58348751909924E-3</v>
+        <v>6.1572323362618503E-3</v>
       </c>
       <c r="J13">
-        <v>7.4425192119921997E-3</v>
+        <v>7.0564391255749596E-3</v>
       </c>
       <c r="K13">
-        <v>8.3315680391470998E-3</v>
+        <v>7.9313586025812396E-3</v>
       </c>
       <c r="L13">
-        <v>9.1704208915144008E-3</v>
+        <v>8.8091339982720694E-3</v>
       </c>
       <c r="M13">
-        <v>1.00329150143684E-2</v>
+        <v>9.6638535941082002E-3</v>
       </c>
       <c r="N13">
-        <v>1.08767489559923E-2</v>
+        <v>1.05200050349102E-2</v>
       </c>
       <c r="O13">
-        <v>1.1726890560218301E-2</v>
+        <v>1.13529007659479E-2</v>
       </c>
       <c r="P13">
-        <v>1.26067470805946E-2</v>
+        <v>1.22259147081727E-2</v>
       </c>
       <c r="Q13">
-        <v>1.4082780948080799E-2</v>
+        <v>1.31121475750497E-2</v>
       </c>
       <c r="R13">
-        <v>1.60084666962764E-2</v>
+        <v>1.49505636745417E-2</v>
       </c>
       <c r="S13">
-        <v>1.8074762087037101E-2</v>
+        <v>1.6955854299593301E-2</v>
       </c>
       <c r="T13">
-        <v>2.02405679481296E-2</v>
+        <v>1.90794360746602E-2</v>
       </c>
       <c r="U13">
-        <v>2.2474421862114301E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+        <v>2.12880732854255E-2</v>
+      </c>
+      <c r="V13">
+        <v>2.36214121426838E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2200</v>
       </c>
@@ -11336,52 +11382,55 @@
         <v>4.58603499272431E-3</v>
       </c>
       <c r="G14">
-        <v>5.0088357947785196E-3</v>
+        <v>4.8760226467833203E-3</v>
       </c>
       <c r="H14">
-        <v>5.46589261685593E-3</v>
+        <v>5.3579574832107197E-3</v>
       </c>
       <c r="I14">
-        <v>6.08420340775779E-3</v>
+        <v>5.7454179034272697E-3</v>
       </c>
       <c r="J14">
-        <v>6.8406866897230403E-3</v>
+        <v>6.5283730581998899E-3</v>
       </c>
       <c r="K14">
-        <v>7.5473706201390697E-3</v>
+        <v>7.2393326864117601E-3</v>
       </c>
       <c r="L14">
-        <v>8.2305926953575997E-3</v>
+        <v>7.9133166364040199E-3</v>
       </c>
       <c r="M14">
-        <v>8.8426597944744108E-3</v>
+        <v>8.5648340038297008E-3</v>
       </c>
       <c r="N14">
-        <v>9.5104391807875003E-3</v>
+        <v>9.1900763958363291E-3</v>
       </c>
       <c r="O14">
-        <v>1.0194540355402701E-2</v>
+        <v>9.8472045248774696E-3</v>
       </c>
       <c r="P14">
-        <v>1.09032149728833E-2</v>
+        <v>1.05353047507202E-2</v>
       </c>
       <c r="Q14">
-        <v>1.2151553085689E-2</v>
+        <v>1.12369862872663E-2</v>
       </c>
       <c r="R14">
-        <v>1.36947987683894E-2</v>
+        <v>1.2733783797712899E-2</v>
       </c>
       <c r="S14">
-        <v>1.52404709685551E-2</v>
+        <v>1.4259654677420901E-2</v>
       </c>
       <c r="T14">
-        <v>1.6791603548254999E-2</v>
+        <v>1.5814272315732E-2</v>
       </c>
       <c r="U14">
-        <v>1.8291017525686001E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+        <v>1.73305729132779E-2</v>
+      </c>
+      <c r="V14">
+        <v>1.88528201708834E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2400</v>
       </c>
@@ -11401,52 +11450,55 @@
         <v>4.1850297566963599E-3</v>
       </c>
       <c r="G15">
-        <v>4.5466243510580298E-3</v>
+        <v>4.4332107403266896E-3</v>
       </c>
       <c r="H15">
-        <v>4.9195873870543196E-3</v>
+        <v>4.8453690373341501E-3</v>
       </c>
       <c r="I15">
-        <v>5.4488165360580803E-3</v>
+        <v>5.1661004866044198E-3</v>
       </c>
       <c r="J15">
-        <v>6.0453231995961504E-3</v>
+        <v>5.8234547165225197E-3</v>
       </c>
       <c r="K15">
-        <v>6.53790394708984E-3</v>
+        <v>6.3351042888227004E-3</v>
       </c>
       <c r="L15">
-        <v>6.9932602613883999E-3</v>
+        <v>6.8088000368178997E-3</v>
       </c>
       <c r="M15">
-        <v>7.4268470288055199E-3</v>
+        <v>7.2466127033667099E-3</v>
       </c>
       <c r="N15">
-        <v>7.8633633581471196E-3</v>
+        <v>7.6907760935528797E-3</v>
       </c>
       <c r="O15">
-        <v>8.3045963363689908E-3</v>
+        <v>8.1243435696646202E-3</v>
       </c>
       <c r="P15">
-        <v>8.7632333556689999E-3</v>
+        <v>8.5592078149398596E-3</v>
       </c>
       <c r="Q15">
-        <v>9.6057419686930903E-3</v>
+        <v>9.02997930282687E-3</v>
       </c>
       <c r="R15">
-        <v>1.0728254912490499E-2</v>
+        <v>1.0071542122198801E-2</v>
       </c>
       <c r="S15">
-        <v>1.2040983179039301E-2</v>
+        <v>1.1232245012401099E-2</v>
       </c>
       <c r="T15">
-        <v>1.3383032730646E-2</v>
+        <v>1.2526052978025099E-2</v>
       </c>
       <c r="U15">
-        <v>1.4741801387796301E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+        <v>1.38246578220178E-2</v>
+      </c>
+      <c r="V15">
+        <v>1.51848899964711E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2600</v>
       </c>
@@ -11466,52 +11518,55 @@
         <v>3.4741195728023502E-3</v>
       </c>
       <c r="G16">
-        <v>3.7437193801981299E-3</v>
+        <v>3.6683825912490701E-3</v>
       </c>
       <c r="H16">
-        <v>4.0467180251112398E-3</v>
+        <v>3.9704217782077396E-3</v>
       </c>
       <c r="I16">
-        <v>4.4616301476812798E-3</v>
+        <v>4.2298261780095098E-3</v>
       </c>
       <c r="J16">
-        <v>4.9395278028662197E-3</v>
+        <v>4.7248662337959898E-3</v>
       </c>
       <c r="K16">
-        <v>5.4079322547737098E-3</v>
+        <v>5.1951223555927297E-3</v>
       </c>
       <c r="L16">
-        <v>5.83671863846086E-3</v>
+        <v>5.6270921622824698E-3</v>
       </c>
       <c r="M16">
-        <v>6.24480448745896E-3</v>
+        <v>6.0413372578479998E-3</v>
       </c>
       <c r="N16">
-        <v>6.6674434596887501E-3</v>
+        <v>6.4526570815748897E-3</v>
       </c>
       <c r="O16">
-        <v>7.1060404609743404E-3</v>
+        <v>6.8728740381898698E-3</v>
       </c>
       <c r="P16">
-        <v>7.5441042367492099E-3</v>
+        <v>7.3058237920528499E-3</v>
       </c>
       <c r="Q16">
-        <v>8.2844353790989499E-3</v>
+        <v>7.7376142089867596E-3</v>
       </c>
       <c r="R16">
-        <v>9.1903565242081198E-3</v>
+        <v>8.6057487818590305E-3</v>
       </c>
       <c r="S16">
-        <v>1.01138717096022E-2</v>
+        <v>9.4856400445384494E-3</v>
       </c>
       <c r="T16">
-        <v>1.1135007904023201E-2</v>
+        <v>1.04146393162539E-2</v>
       </c>
       <c r="U16">
-        <v>1.2234657744078401E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+        <v>1.1444615605746E-2</v>
+      </c>
+      <c r="V16">
+        <v>1.2511514099768899E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2800</v>
       </c>
@@ -11531,52 +11586,55 @@
         <v>3.0961765763120402E-3</v>
       </c>
       <c r="G17">
-        <v>3.3549486500487201E-3</v>
+        <v>3.2683359331646998E-3</v>
       </c>
       <c r="H17">
-        <v>3.6211459743776E-3</v>
+        <v>3.5593418213439401E-3</v>
       </c>
       <c r="I17">
-        <v>3.9778758031120401E-3</v>
+        <v>3.7733588965167398E-3</v>
       </c>
       <c r="J17">
-        <v>4.42838970230115E-3</v>
+        <v>4.2416785238740297E-3</v>
       </c>
       <c r="K17">
-        <v>4.7681767633175696E-3</v>
+        <v>4.6277297423341097E-3</v>
       </c>
       <c r="L17">
-        <v>5.0889093091002202E-3</v>
+        <v>4.9435148300407796E-3</v>
       </c>
       <c r="M17">
-        <v>5.3922597414590503E-3</v>
+        <v>5.2559459613999099E-3</v>
       </c>
       <c r="N17">
-        <v>5.6743948902942803E-3</v>
+        <v>5.5393185093228501E-3</v>
       </c>
       <c r="O17">
-        <v>5.9603222442285702E-3</v>
+        <v>5.8088931040049903E-3</v>
       </c>
       <c r="P17">
-        <v>6.2609123175225399E-3</v>
+        <v>6.1030247117772798E-3</v>
       </c>
       <c r="Q17">
-        <v>6.7503539759441403E-3</v>
+        <v>6.3918098753678399E-3</v>
       </c>
       <c r="R17">
-        <v>7.3306106226517101E-3</v>
+        <v>6.9598169982961998E-3</v>
       </c>
       <c r="S17">
-        <v>7.9217293459309807E-3</v>
+        <v>7.52984520327552E-3</v>
       </c>
       <c r="T17">
-        <v>8.5234744196706E-3</v>
+        <v>8.1070039628515795E-3</v>
       </c>
       <c r="U17">
-        <v>9.1422181048141701E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+        <v>8.6952565877449501E-3</v>
+      </c>
+      <c r="V17">
+        <v>9.3013470638119693E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>3000</v>
       </c>
@@ -11596,52 +11654,55 @@
         <v>3.2544943460999999E-3</v>
       </c>
       <c r="G18">
-        <v>3.49311427554837E-3</v>
+        <v>3.4301482714634299E-3</v>
       </c>
       <c r="H18">
-        <v>3.7128728519196601E-3</v>
+        <v>3.66147813298168E-3</v>
       </c>
       <c r="I18">
-        <v>3.9890925898964699E-3</v>
+        <v>3.84511089870185E-3</v>
       </c>
       <c r="J18">
-        <v>4.3427427599982398E-3</v>
+        <v>4.2293968181080699E-3</v>
       </c>
       <c r="K18">
-        <v>4.6677646507276198E-3</v>
+        <v>4.57097338598872E-3</v>
       </c>
       <c r="L18">
-        <v>4.9254761529498696E-3</v>
+        <v>4.8377890937833599E-3</v>
       </c>
       <c r="M18">
-        <v>5.1688602709166701E-3</v>
+        <v>5.0690315083921902E-3</v>
       </c>
       <c r="N18">
-        <v>5.3787904067834E-3</v>
+        <v>5.2900965237387097E-3</v>
       </c>
       <c r="O18">
-        <v>5.5763147768466397E-3</v>
+        <v>5.4924237897170198E-3</v>
       </c>
       <c r="P18">
-        <v>5.7625442283484197E-3</v>
+        <v>5.6827023230267603E-3</v>
       </c>
       <c r="Q18">
-        <v>6.0402298439026399E-3</v>
+        <v>5.8631547619554898E-3</v>
       </c>
       <c r="R18">
-        <v>6.3817045134801397E-3</v>
+        <v>6.2086477716923796E-3</v>
       </c>
       <c r="S18">
-        <v>6.7361946595524197E-3</v>
+        <v>6.5342845426672701E-3</v>
       </c>
       <c r="T18">
-        <v>7.0640284537899101E-3</v>
+        <v>6.8771722017402096E-3</v>
       </c>
       <c r="U18">
-        <v>7.4001335371845197E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+        <v>7.1953744784464396E-3</v>
+      </c>
+      <c r="V18">
+        <v>7.51951932480801E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3200</v>
       </c>
@@ -11661,57 +11722,60 @@
         <v>2.5923270422694702E-3</v>
       </c>
       <c r="G19">
-        <v>2.7931911898271501E-3</v>
+        <v>2.73217237852334E-3</v>
       </c>
       <c r="H19">
-        <v>3.0314950756893302E-3</v>
+        <v>2.97477936792032E-3</v>
       </c>
       <c r="I19">
-        <v>3.3909618119616898E-3</v>
+        <v>3.18395458292569E-3</v>
       </c>
       <c r="J19">
-        <v>3.79285508263856E-3</v>
+        <v>3.6142548667002401E-3</v>
       </c>
       <c r="K19">
-        <v>4.1265192320570398E-3</v>
+        <v>3.9725278978169701E-3</v>
       </c>
       <c r="L19">
-        <v>4.4101168845079204E-3</v>
+        <v>4.2810739200041404E-3</v>
       </c>
       <c r="M19">
-        <v>4.6495234192237504E-3</v>
+        <v>4.5396928761573703E-3</v>
       </c>
       <c r="N19">
-        <v>4.8729783383058096E-3</v>
+        <v>4.7802979749314196E-3</v>
       </c>
       <c r="O19">
-        <v>5.06482222712975E-3</v>
+        <v>4.9810865762967499E-3</v>
       </c>
       <c r="P19">
-        <v>5.24561134710073E-3</v>
+        <v>5.1667339282071602E-3</v>
       </c>
       <c r="Q19">
-        <v>5.5519288909494698E-3</v>
+        <v>5.36019544595612E-3</v>
       </c>
       <c r="R19">
-        <v>5.93484337556214E-3</v>
+        <v>5.7316973922301997E-3</v>
       </c>
       <c r="S19">
-        <v>6.3282766470831699E-3</v>
+        <v>6.1312449371934297E-3</v>
       </c>
       <c r="T19">
-        <v>6.71496598837473E-3</v>
+        <v>6.5228885300049897E-3</v>
       </c>
       <c r="U19">
-        <v>7.0556252079185802E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+        <v>6.87287151230435E-3</v>
+      </c>
+      <c r="V19">
+        <v>7.16511775341725E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -11775,8 +11839,11 @@
       <c r="U22" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>0</v>
       </c>
@@ -11796,52 +11863,55 @@
         <v>2.4928992852435401E-2</v>
       </c>
       <c r="G23">
-        <v>2.8119346704281001E-2</v>
+        <v>2.7018098500062499E-2</v>
       </c>
       <c r="H23">
-        <v>3.1310509363493798E-2</v>
+        <v>3.0415025417613699E-2</v>
       </c>
       <c r="I23">
-        <v>3.5585022862650903E-2</v>
+        <v>3.3131451393083503E-2</v>
       </c>
       <c r="J23">
-        <v>3.9588634830836203E-2</v>
+        <v>3.8101632763529798E-2</v>
       </c>
       <c r="K23">
-        <v>4.2835066321934998E-2</v>
+        <v>4.1678514080609401E-2</v>
       </c>
       <c r="L23">
-        <v>4.6065354330191099E-2</v>
+        <v>4.4953961137188699E-2</v>
       </c>
       <c r="M23">
-        <v>4.9295895944087599E-2</v>
+        <v>4.8222446883184798E-2</v>
       </c>
       <c r="N23">
-        <v>5.2379339353908497E-2</v>
+        <v>5.1345015446024697E-2</v>
       </c>
       <c r="O23">
-        <v>5.5270372131739597E-2</v>
+        <v>5.4282042269228697E-2</v>
       </c>
       <c r="P23">
-        <v>5.7879943670525298E-2</v>
+        <v>5.6979090442653098E-2</v>
       </c>
       <c r="Q23">
-        <v>6.1390830755874398E-2</v>
+        <v>5.9390234685265803E-2</v>
       </c>
       <c r="R23">
-        <v>6.5953578541177504E-2</v>
+        <v>6.3871839268067901E-2</v>
       </c>
       <c r="S23">
-        <v>7.0544937717424094E-2</v>
+        <v>6.8368182518005999E-2</v>
       </c>
       <c r="T23">
-        <v>7.5278035897977102E-2</v>
+        <v>7.3002395061654596E-2</v>
       </c>
       <c r="U23">
-        <v>7.9544325691581805E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+        <v>7.74958816032911E-2</v>
+      </c>
+      <c r="V23">
+        <v>8.1618176270488105E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>200</v>
       </c>
@@ -11861,52 +11931,55 @@
         <v>2.9297988584816099E-2</v>
       </c>
       <c r="G24">
-        <v>3.3089755818678797E-2</v>
+        <v>3.1811552993343602E-2</v>
       </c>
       <c r="H24">
-        <v>3.6955787683625403E-2</v>
+        <v>3.6029819359966297E-2</v>
       </c>
       <c r="I24">
-        <v>4.2125693582890901E-2</v>
+        <v>3.9324275450673303E-2</v>
       </c>
       <c r="J24">
-        <v>4.7761695896438999E-2</v>
+        <v>4.5654571663088499E-2</v>
       </c>
       <c r="K24">
-        <v>5.2254861325154799E-2</v>
+        <v>5.04657597233465E-2</v>
       </c>
       <c r="L24">
-        <v>5.5931322490869302E-2</v>
+        <v>5.4450886321603602E-2</v>
       </c>
       <c r="M24">
-        <v>5.91547550607694E-2</v>
+        <v>5.78959688569569E-2</v>
       </c>
       <c r="N24">
-        <v>6.1941465755832099E-2</v>
+        <v>6.0804687033270098E-2</v>
       </c>
       <c r="O24">
-        <v>6.4432951655897006E-2</v>
+        <v>6.3299300965743793E-2</v>
       </c>
       <c r="P24">
-        <v>6.6829463425826505E-2</v>
+        <v>6.5612436644190003E-2</v>
       </c>
       <c r="Q24">
-        <v>7.0795719546285094E-2</v>
+        <v>6.7847563812243494E-2</v>
       </c>
       <c r="R24">
-        <v>7.5577781096270003E-2</v>
+        <v>7.2427117089289006E-2</v>
       </c>
       <c r="S24">
-        <v>8.0314608960339498E-2</v>
+        <v>7.7254548917325597E-2</v>
       </c>
       <c r="T24">
-        <v>8.4911843030011397E-2</v>
+        <v>8.2055578268759394E-2</v>
       </c>
       <c r="U24">
-        <v>8.9611466531378803E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+        <v>8.6868748894717199E-2</v>
+      </c>
+      <c r="V24">
+        <v>9.1769544063040304E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>400</v>
       </c>
@@ -11926,52 +11999,55 @@
         <v>2.9449200753594602E-2</v>
       </c>
       <c r="G25">
-        <v>3.3874715148198301E-2</v>
+        <v>3.2377473620851902E-2</v>
       </c>
       <c r="H25">
-        <v>3.8317607474934498E-2</v>
+        <v>3.71651873763858E-2</v>
       </c>
       <c r="I25">
-        <v>4.4581830114819698E-2</v>
+        <v>4.10490447652372E-2</v>
       </c>
       <c r="J25">
-        <v>5.1064277664861803E-2</v>
+        <v>4.8511413535588702E-2</v>
       </c>
       <c r="K25">
-        <v>5.6046616782575699E-2</v>
+        <v>5.4250385437752499E-2</v>
       </c>
       <c r="L25">
-        <v>6.0074099886079098E-2</v>
+        <v>5.8648501272408698E-2</v>
       </c>
       <c r="M25">
-        <v>6.3384814060752095E-2</v>
+        <v>6.2146689438932298E-2</v>
       </c>
       <c r="N25">
-        <v>6.6410702218895099E-2</v>
+        <v>6.51764248918099E-2</v>
       </c>
       <c r="O25">
-        <v>6.9278315387534303E-2</v>
+        <v>6.8012319934175794E-2</v>
       </c>
       <c r="P25">
-        <v>7.2131274503755297E-2</v>
+        <v>7.0758563178245304E-2</v>
       </c>
       <c r="Q25">
-        <v>7.6638859031362402E-2</v>
+        <v>7.3546894658009496E-2</v>
       </c>
       <c r="R25">
-        <v>8.1835526761410898E-2</v>
+        <v>7.8885489771282402E-2</v>
       </c>
       <c r="S25">
-        <v>8.6900004118940805E-2</v>
+        <v>8.4107713363639605E-2</v>
       </c>
       <c r="T25">
-        <v>9.1782091447107E-2</v>
+        <v>8.9125011622755004E-2</v>
       </c>
       <c r="U25">
-        <v>9.6172269583197204E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+        <v>9.3778265988506998E-2</v>
+      </c>
+      <c r="V25">
+        <v>9.8000410562248105E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>600</v>
       </c>
@@ -11991,52 +12067,55 @@
         <v>2.6124787960196301E-2</v>
       </c>
       <c r="G26">
-        <v>3.0021665295670501E-2</v>
+        <v>2.8691997879286699E-2</v>
       </c>
       <c r="H26">
-        <v>3.45398994279573E-2</v>
+        <v>3.3391287999637698E-2</v>
       </c>
       <c r="I26">
-        <v>4.1098448310955403E-2</v>
+        <v>3.7429269145320701E-2</v>
       </c>
       <c r="J26">
-        <v>4.8274111202229401E-2</v>
+        <v>4.56029324511769E-2</v>
       </c>
       <c r="K26">
-        <v>5.4401686659847702E-2</v>
+        <v>5.2172486201715003E-2</v>
       </c>
       <c r="L26">
-        <v>5.9863866361799599E-2</v>
+        <v>5.78812788504647E-2</v>
       </c>
       <c r="M26">
-        <v>6.47217382798604E-2</v>
+        <v>6.2927460640970198E-2</v>
       </c>
       <c r="N26">
-        <v>6.8981299304012103E-2</v>
+        <v>6.7311513780691196E-2</v>
       </c>
       <c r="O26">
-        <v>7.2778776453815794E-2</v>
+        <v>7.1178774583383897E-2</v>
       </c>
       <c r="P26">
-        <v>7.6316864303654197E-2</v>
+        <v>7.4768184485391395E-2</v>
       </c>
       <c r="Q26">
-        <v>8.1388562144859206E-2</v>
+        <v>7.8159556776160197E-2</v>
       </c>
       <c r="R26">
-        <v>8.7341639769822094E-2</v>
+        <v>8.4435442070542793E-2</v>
       </c>
       <c r="S26">
-        <v>9.2502349248992699E-2</v>
+        <v>8.98306892547968E-2</v>
       </c>
       <c r="T26">
-        <v>9.67636166361317E-2</v>
+        <v>9.4444964292308295E-2</v>
       </c>
       <c r="U26">
-        <v>0.100176415641216</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+        <v>9.8173050486944205E-2</v>
+      </c>
+      <c r="V26">
+        <v>0.101211263058722</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>800</v>
       </c>
@@ -12056,52 +12135,55 @@
         <v>2.41329031063959E-2</v>
       </c>
       <c r="G27">
-        <v>2.7867583764623699E-2</v>
+        <v>2.66214466584066E-2</v>
       </c>
       <c r="H27">
-        <v>3.2173623619856498E-2</v>
+        <v>3.1111726168012398E-2</v>
       </c>
       <c r="I27">
-        <v>3.8749754633044697E-2</v>
+        <v>3.5018441955195601E-2</v>
       </c>
       <c r="J27">
-        <v>4.6801029472108097E-2</v>
+        <v>4.3699425217403602E-2</v>
       </c>
       <c r="K27">
-        <v>5.3648995114494301E-2</v>
+        <v>5.0973657987889998E-2</v>
       </c>
       <c r="L27">
-        <v>5.9620881267163299E-2</v>
+        <v>5.71248103415068E-2</v>
       </c>
       <c r="M27">
-        <v>6.5055220656814905E-2</v>
+        <v>6.2712786984010296E-2</v>
       </c>
       <c r="N27">
-        <v>7.0122434571855102E-2</v>
+        <v>6.7889680288941504E-2</v>
       </c>
       <c r="O27">
-        <v>7.4703603530498097E-2</v>
+        <v>7.2647873285594994E-2</v>
       </c>
       <c r="P27">
-        <v>7.8784102868915906E-2</v>
+        <v>7.6908666660509897E-2</v>
       </c>
       <c r="Q27">
-        <v>8.4373391074117607E-2</v>
+        <v>8.0676492005573003E-2</v>
       </c>
       <c r="R27">
-        <v>8.9977442541955097E-2</v>
+        <v>8.6911787771613694E-2</v>
       </c>
       <c r="S27">
-        <v>9.4472742472880206E-2</v>
+        <v>9.1808265858378202E-2</v>
       </c>
       <c r="T27">
-        <v>9.8196440593297601E-2</v>
+        <v>9.5878669328901003E-2</v>
       </c>
       <c r="U27">
-        <v>0.101362453149896</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+        <v>9.9308951825095304E-2</v>
+      </c>
+      <c r="V27">
+        <v>0.102255113653083</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1000</v>
       </c>
@@ -12121,52 +12203,55 @@
         <v>2.0551422294838799E-2</v>
       </c>
       <c r="G28">
-        <v>2.3620522336651999E-2</v>
+        <v>2.26243206827496E-2</v>
       </c>
       <c r="H28">
-        <v>2.7336319532038699E-2</v>
+        <v>2.64186653867697E-2</v>
       </c>
       <c r="I28">
-        <v>3.3685037826524301E-2</v>
+        <v>3.0077709530489799E-2</v>
       </c>
       <c r="J28">
-        <v>4.1796225314279803E-2</v>
+        <v>3.8606168181907298E-2</v>
       </c>
       <c r="K28">
-        <v>4.9180164620961503E-2</v>
+        <v>4.6325322655697498E-2</v>
       </c>
       <c r="L28">
-        <v>5.5805810675715398E-2</v>
+        <v>5.3218480016287102E-2</v>
       </c>
       <c r="M28">
-        <v>6.1755244366895203E-2</v>
+        <v>5.9400122856632202E-2</v>
       </c>
       <c r="N28">
-        <v>6.7158827186442296E-2</v>
+        <v>6.5025078327409697E-2</v>
       </c>
       <c r="O28">
-        <v>7.2020762941853E-2</v>
+        <v>7.00855174596728E-2</v>
       </c>
       <c r="P28">
-        <v>7.6385249960030696E-2</v>
+        <v>7.4612588153479098E-2</v>
       </c>
       <c r="Q28">
-        <v>8.2128033190975294E-2</v>
+        <v>7.8683862194142695E-2</v>
       </c>
       <c r="R28">
-        <v>8.8347327736008993E-2</v>
+        <v>8.5479724199076595E-2</v>
       </c>
       <c r="S28">
-        <v>9.3372567741746695E-2</v>
+        <v>9.0892478112167593E-2</v>
       </c>
       <c r="T28">
-        <v>9.7527001627022603E-2</v>
+        <v>9.5280980008818197E-2</v>
       </c>
       <c r="U28">
-        <v>0.10100796183686001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+        <v>9.8982414042840194E-2</v>
+      </c>
+      <c r="V28">
+        <v>0.102133885412326</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1200</v>
       </c>
@@ -12186,52 +12271,55 @@
         <v>1.8120699791137399E-2</v>
       </c>
       <c r="G29">
-        <v>2.0650629508439999E-2</v>
+        <v>1.983056457188E-2</v>
       </c>
       <c r="H29">
-        <v>2.3587836933317001E-2</v>
+        <v>2.2857853307782599E-2</v>
       </c>
       <c r="I29">
-        <v>2.8618991781883499E-2</v>
+        <v>2.56559253198454E-2</v>
       </c>
       <c r="J29">
-        <v>3.55599890883838E-2</v>
+        <v>3.2726947664056601E-2</v>
       </c>
       <c r="K29">
-        <v>4.24247838908468E-2</v>
+        <v>3.9656933676049597E-2</v>
       </c>
       <c r="L29">
-        <v>4.89689231922249E-2</v>
+        <v>4.6355122621861401E-2</v>
       </c>
       <c r="M29">
-        <v>5.5080867220368299E-2</v>
+        <v>5.2575896176778297E-2</v>
       </c>
       <c r="N29">
-        <v>6.0691131087658598E-2</v>
+        <v>5.8406444171231899E-2</v>
       </c>
       <c r="O29">
-        <v>6.5922808907155503E-2</v>
+        <v>6.3805753009484004E-2</v>
       </c>
       <c r="P29">
-        <v>7.06340809307235E-2</v>
+        <v>6.8781919813708806E-2</v>
       </c>
       <c r="Q29">
-        <v>7.6965534347690698E-2</v>
+        <v>7.3272161747038295E-2</v>
       </c>
       <c r="R29">
-        <v>8.4456337605260598E-2</v>
+        <v>8.1334764889222894E-2</v>
       </c>
       <c r="S29">
-        <v>9.0630793789426498E-2</v>
+        <v>8.8104874273541203E-2</v>
       </c>
       <c r="T29">
-        <v>9.5519146915241104E-2</v>
+        <v>9.3557986596136497E-2</v>
       </c>
       <c r="U29">
-        <v>9.9408833503150301E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+        <v>9.7878219197970601E-2</v>
+      </c>
+      <c r="V29">
+        <v>0.10134284723695999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1400</v>
       </c>
@@ -12251,52 +12339,55 @@
         <v>1.37498073400911E-2</v>
       </c>
       <c r="G30">
-        <v>1.5461795375087101E-2</v>
+        <v>1.4935050044263E-2</v>
       </c>
       <c r="H30">
-        <v>1.7475699652085602E-2</v>
+        <v>1.70299217583759E-2</v>
       </c>
       <c r="I30">
-        <v>2.07521365958881E-2</v>
+        <v>1.89599910805574E-2</v>
       </c>
       <c r="J30">
-        <v>2.5190541569855202E-2</v>
+        <v>2.3636345048629999E-2</v>
       </c>
       <c r="K30">
-        <v>2.9455301085823601E-2</v>
+        <v>2.8019500005972801E-2</v>
       </c>
       <c r="L30">
-        <v>3.39124223884315E-2</v>
+        <v>3.2501286037818003E-2</v>
       </c>
       <c r="M30">
-        <v>3.8599818377476301E-2</v>
+        <v>3.7136944168130501E-2</v>
       </c>
       <c r="N30">
-        <v>4.3370367246499099E-2</v>
+        <v>4.1867012408574003E-2</v>
       </c>
       <c r="O30">
-        <v>4.8133374000574103E-2</v>
+        <v>4.6650602022088497E-2</v>
       </c>
       <c r="P30">
-        <v>5.27842040954127E-2</v>
+        <v>5.1346136283663101E-2</v>
       </c>
       <c r="Q30">
-        <v>5.9022177784875098E-2</v>
+        <v>5.5930925352192497E-2</v>
       </c>
       <c r="R30">
-        <v>6.7345873993403693E-2</v>
+        <v>6.4699939622693894E-2</v>
       </c>
       <c r="S30">
-        <v>7.4857158533889606E-2</v>
+        <v>7.25471442825006E-2</v>
       </c>
       <c r="T30">
-        <v>8.1584157924126197E-2</v>
+        <v>7.9559139368241605E-2</v>
       </c>
       <c r="U30">
-        <v>8.7460834646814603E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+        <v>8.5749151954805897E-2</v>
+      </c>
+      <c r="V30">
+        <v>9.1089760080248203E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>1600</v>
       </c>
@@ -12316,52 +12407,55 @@
         <v>1.07640812981419E-2</v>
       </c>
       <c r="G31">
-        <v>1.1786666913730899E-2</v>
+        <v>1.14566790777146E-2</v>
       </c>
       <c r="H31">
-        <v>1.29842942477769E-2</v>
+        <v>1.26732972416921E-2</v>
       </c>
       <c r="I31">
-        <v>1.5110006036610399E-2</v>
+        <v>1.3791906719779401E-2</v>
       </c>
       <c r="J31">
-        <v>1.7794385122449699E-2</v>
+        <v>1.65849446019345E-2</v>
       </c>
       <c r="K31">
-        <v>2.0587562090441502E-2</v>
+        <v>1.9344109215133298E-2</v>
       </c>
       <c r="L31">
-        <v>2.3376622238599602E-2</v>
+        <v>2.2131286659124699E-2</v>
       </c>
       <c r="M31">
-        <v>2.62326920130494E-2</v>
+        <v>2.4946746126488301E-2</v>
       </c>
       <c r="N31">
-        <v>2.9090809466381699E-2</v>
+        <v>2.7836215839141299E-2</v>
       </c>
       <c r="O31">
-        <v>3.1972221709476403E-2</v>
+        <v>3.0733130809992602E-2</v>
       </c>
       <c r="P31">
-        <v>3.4884487354432003E-2</v>
+        <v>3.36863655952232E-2</v>
       </c>
       <c r="Q31">
-        <v>3.9328509891236797E-2</v>
+        <v>3.6701896116470602E-2</v>
       </c>
       <c r="R31">
-        <v>4.5292913482399201E-2</v>
+        <v>4.2949925864753699E-2</v>
       </c>
       <c r="S31">
-        <v>5.1369752267520899E-2</v>
+        <v>4.9245649803805698E-2</v>
       </c>
       <c r="T31">
-        <v>5.7315823815861797E-2</v>
+        <v>5.54507922388148E-2</v>
       </c>
       <c r="U31">
-        <v>6.3097237870668996E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+        <v>6.1478414068815802E-2</v>
+      </c>
+      <c r="V31">
+        <v>6.7230844702737699E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1800</v>
       </c>
@@ -12381,52 +12475,55 @@
         <v>7.2710712277010599E-3</v>
       </c>
       <c r="G32">
-        <v>8.0705678882842594E-3</v>
+        <v>7.82297039647031E-3</v>
       </c>
       <c r="H32">
-        <v>8.9829825370242103E-3</v>
+        <v>8.7645400884232404E-3</v>
       </c>
       <c r="I32">
-        <v>1.04491561000762E-2</v>
+        <v>9.5841819551627499E-3</v>
       </c>
       <c r="J32">
-        <v>1.2385221955039299E-2</v>
+        <v>1.15739285314086E-2</v>
       </c>
       <c r="K32">
-        <v>1.41212120971755E-2</v>
+        <v>1.3399360468022901E-2</v>
       </c>
       <c r="L32">
-        <v>1.5800374055776799E-2</v>
+        <v>1.50913042923365E-2</v>
       </c>
       <c r="M32">
-        <v>1.7546583393230099E-2</v>
+        <v>1.6782576349906202E-2</v>
       </c>
       <c r="N32">
-        <v>1.9247554244331801E-2</v>
+        <v>1.8529324217079701E-2</v>
       </c>
       <c r="O32">
-        <v>2.0947616208103301E-2</v>
+        <v>2.02123258909413E-2</v>
       </c>
       <c r="P32">
-        <v>2.26501901466695E-2</v>
+        <v>2.1911400057401598E-2</v>
       </c>
       <c r="Q32">
-        <v>2.53062119563408E-2</v>
+        <v>2.3622770573227501E-2</v>
       </c>
       <c r="R32">
-        <v>2.88125650975968E-2</v>
+        <v>2.7167622006370601E-2</v>
       </c>
       <c r="S32">
-        <v>3.2407304659723302E-2</v>
+        <v>3.0872474393074299E-2</v>
       </c>
       <c r="T32">
-        <v>3.6057887910173697E-2</v>
+        <v>3.4654560564383402E-2</v>
       </c>
       <c r="U32">
-        <v>3.9827490889408797E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
+        <v>3.8466489685042002E-2</v>
+      </c>
+      <c r="V32">
+        <v>4.2396833251402602E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>2000</v>
       </c>
@@ -12446,52 +12543,55 @@
         <v>5.6726036304868502E-3</v>
       </c>
       <c r="G33">
-        <v>6.2312119083571902E-3</v>
+        <v>6.03843252181855E-3</v>
       </c>
       <c r="H33">
-        <v>6.8223428175039702E-3</v>
+        <v>6.6735668006148701E-3</v>
       </c>
       <c r="I33">
-        <v>7.6968201051108697E-3</v>
+        <v>7.1925650616153801E-3</v>
       </c>
       <c r="J33">
-        <v>8.8776233088849795E-3</v>
+        <v>8.3581589760826705E-3</v>
       </c>
       <c r="K33">
-        <v>9.8695587151201893E-3</v>
+        <v>9.4183992378298696E-3</v>
       </c>
       <c r="L33">
-        <v>1.0793846521219499E-2</v>
+        <v>1.03492143762538E-2</v>
       </c>
       <c r="M33">
-        <v>1.17519731097059E-2</v>
+        <v>1.12941452990443E-2</v>
       </c>
       <c r="N33">
-        <v>1.27321630573109E-2</v>
+        <v>1.22712662190636E-2</v>
       </c>
       <c r="O33">
-        <v>1.3794852456184101E-2</v>
+        <v>1.3301823468040401E-2</v>
       </c>
       <c r="P33">
-        <v>1.48808007923165E-2</v>
+        <v>1.43639157285281E-2</v>
       </c>
       <c r="Q33">
-        <v>1.66838446132981E-2</v>
+        <v>1.5444913402206601E-2</v>
       </c>
       <c r="R33">
-        <v>1.91396551754992E-2</v>
+        <v>1.78080115171305E-2</v>
       </c>
       <c r="S33">
-        <v>2.1706234208420602E-2</v>
+        <v>2.0384075179355501E-2</v>
       </c>
       <c r="T33">
-        <v>2.4261602256535099E-2</v>
+        <v>2.2997791718270901E-2</v>
       </c>
       <c r="U33">
-        <v>2.6763322329417302E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
+        <v>2.5616438121240301E-2</v>
+      </c>
+      <c r="V33">
+        <v>2.8185828793532899E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>2200</v>
       </c>
@@ -12511,52 +12611,55 @@
         <v>4.8625252111151301E-3</v>
       </c>
       <c r="G34">
-        <v>5.35707894089034E-3</v>
+        <v>5.1875505941350302E-3</v>
       </c>
       <c r="H34">
-        <v>5.86264419984198E-3</v>
+        <v>5.7337173087899799E-3</v>
       </c>
       <c r="I34">
-        <v>6.57163506864123E-3</v>
+        <v>6.1462031683480198E-3</v>
       </c>
       <c r="J34">
-        <v>7.3972535825626599E-3</v>
+        <v>7.0141053027015197E-3</v>
       </c>
       <c r="K34">
-        <v>8.1339128580798399E-3</v>
+        <v>7.7850826748743999E-3</v>
       </c>
       <c r="L34">
-        <v>8.8347043406659404E-3</v>
+        <v>8.4915732196071802E-3</v>
       </c>
       <c r="M34">
-        <v>9.5435212540627406E-3</v>
+        <v>9.1728288030513E-3</v>
       </c>
       <c r="N34">
-        <v>1.02972068571389E-2</v>
+        <v>9.8926023607104601E-3</v>
       </c>
       <c r="O34">
-        <v>1.10546504803231E-2</v>
+        <v>1.06461390465425E-2</v>
       </c>
       <c r="P34">
-        <v>1.18264974719571E-2</v>
+        <v>1.1397814596300199E-2</v>
       </c>
       <c r="Q34">
-        <v>1.31795237862668E-2</v>
+        <v>1.2160981448364401E-2</v>
       </c>
       <c r="R34">
-        <v>1.48831983452945E-2</v>
+        <v>1.3760562780707799E-2</v>
       </c>
       <c r="S34">
-        <v>1.6663585313422501E-2</v>
+        <v>1.54710328071414E-2</v>
       </c>
       <c r="T34">
-        <v>1.8441251347452E-2</v>
+        <v>1.7242704776968001E-2</v>
       </c>
       <c r="U34">
-        <v>2.01911915598494E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+        <v>1.9011555828110399E-2</v>
+      </c>
+      <c r="V34">
+        <v>2.0781815625915401E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2400</v>
       </c>
@@ -12576,52 +12679,55 @@
         <v>4.3234754288564202E-3</v>
       </c>
       <c r="G35">
-        <v>4.69384416927716E-3</v>
+        <v>4.5666130751730004E-3</v>
       </c>
       <c r="H35">
-        <v>5.05595596539124E-3</v>
+        <v>4.9644277052514297E-3</v>
       </c>
       <c r="I35">
-        <v>5.6237814495438999E-3</v>
+        <v>5.28707125680052E-3</v>
       </c>
       <c r="J35">
-        <v>6.2505196298880397E-3</v>
+        <v>5.9997199274277298E-3</v>
       </c>
       <c r="K35">
-        <v>6.78787383362295E-3</v>
+        <v>6.5323485724513497E-3</v>
       </c>
       <c r="L35">
-        <v>7.3027928887334304E-3</v>
+        <v>7.0520814921849802E-3</v>
       </c>
       <c r="M35">
-        <v>7.7951717970674503E-3</v>
+        <v>7.5711720038958603E-3</v>
       </c>
       <c r="N35">
-        <v>8.2676997381961794E-3</v>
+        <v>8.0447694094327102E-3</v>
       </c>
       <c r="O35">
-        <v>8.7564753158672504E-3</v>
+        <v>8.5350191056796105E-3</v>
       </c>
       <c r="P35">
-        <v>9.2471664364826307E-3</v>
+        <v>9.0162639342242206E-3</v>
       </c>
       <c r="Q35">
-        <v>1.01026101422492E-2</v>
+        <v>9.5078086366643891E-3</v>
       </c>
       <c r="R35">
-        <v>1.1302293856209501E-2</v>
+        <v>1.0569194226866601E-2</v>
       </c>
       <c r="S35">
-        <v>1.2655308898223E-2</v>
+        <v>1.17955928532917E-2</v>
       </c>
       <c r="T35">
-        <v>1.4105951631842001E-2</v>
+        <v>1.316669591787E-2</v>
       </c>
       <c r="U35">
-        <v>1.5563671558792401E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
+        <v>1.4589162277097801E-2</v>
+      </c>
+      <c r="V35">
+        <v>1.6052390553597001E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>2600</v>
       </c>
@@ -12641,52 +12747,55 @@
         <v>3.4045344681912799E-3</v>
       </c>
       <c r="G36">
-        <v>3.6590581464361199E-3</v>
+        <v>3.5796299559437798E-3</v>
       </c>
       <c r="H36">
-        <v>3.9483737406558099E-3</v>
+        <v>3.8772936401648898E-3</v>
       </c>
       <c r="I36">
-        <v>4.3956467261410297E-3</v>
+        <v>4.1294660671573301E-3</v>
       </c>
       <c r="J36">
-        <v>4.9355843041234797E-3</v>
+        <v>4.6955008523607497E-3</v>
       </c>
       <c r="K36">
-        <v>5.4068789755197296E-3</v>
+        <v>5.1670731735513897E-3</v>
       </c>
       <c r="L36">
-        <v>5.8475467561915403E-3</v>
+        <v>5.6174711398045696E-3</v>
       </c>
       <c r="M36">
-        <v>6.28065257827644E-3</v>
+        <v>6.05486824198907E-3</v>
       </c>
       <c r="N36">
-        <v>6.7104114669824999E-3</v>
+        <v>6.4873808586246298E-3</v>
       </c>
       <c r="O36">
-        <v>7.1308826153071297E-3</v>
+        <v>6.9188658102356101E-3</v>
       </c>
       <c r="P36">
-        <v>7.55655517418576E-3</v>
+        <v>7.3452695071603603E-3</v>
       </c>
       <c r="Q36">
-        <v>8.2853685417240992E-3</v>
+        <v>7.7627637876449699E-3</v>
       </c>
       <c r="R36">
-        <v>9.2089080590289692E-3</v>
+        <v>8.6152373296020292E-3</v>
       </c>
       <c r="S36">
-        <v>1.0230461440997001E-2</v>
+        <v>9.5647656504738408E-3</v>
       </c>
       <c r="T36">
-        <v>1.1276474274579101E-2</v>
+        <v>1.05543943542742E-2</v>
       </c>
       <c r="U36">
-        <v>1.23684975673818E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
+        <v>1.1562214161007899E-2</v>
+      </c>
+      <c r="V36">
+        <v>1.26406517720449E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>2800</v>
       </c>
@@ -12706,52 +12815,55 @@
         <v>3.0970246190701899E-3</v>
       </c>
       <c r="G37">
-        <v>3.32647447525437E-3</v>
+        <v>3.2605819085168601E-3</v>
       </c>
       <c r="H37">
-        <v>3.5746909132014998E-3</v>
+        <v>3.51379018509749E-3</v>
       </c>
       <c r="I37">
-        <v>3.9230360712480703E-3</v>
+        <v>3.7274432267779601E-3</v>
       </c>
       <c r="J37">
-        <v>4.3006689626578802E-3</v>
+        <v>4.1509938266653303E-3</v>
       </c>
       <c r="K37">
-        <v>4.6361045059092202E-3</v>
+        <v>4.4820275270925402E-3</v>
       </c>
       <c r="L37">
-        <v>4.9652277333847496E-3</v>
+        <v>4.8188724586086997E-3</v>
       </c>
       <c r="M37">
-        <v>5.2890477635346798E-3</v>
+        <v>5.1413792314319801E-3</v>
       </c>
       <c r="N37">
-        <v>5.5850764070500504E-3</v>
+        <v>5.44659358806923E-3</v>
       </c>
       <c r="O37">
-        <v>5.8620945500877002E-3</v>
+        <v>5.7289202482154701E-3</v>
       </c>
       <c r="P37">
-        <v>6.1531606584375896E-3</v>
+        <v>6.0038064046996596E-3</v>
       </c>
       <c r="Q37">
-        <v>6.6325151002171699E-3</v>
+        <v>6.2946474242706798E-3</v>
       </c>
       <c r="R37">
-        <v>7.2015227628857703E-3</v>
+        <v>6.8675177385184001E-3</v>
       </c>
       <c r="S37">
-        <v>7.7801447000362704E-3</v>
+        <v>7.4123023677657397E-3</v>
       </c>
       <c r="T37">
-        <v>8.3860646535419206E-3</v>
+        <v>7.9786385999382793E-3</v>
       </c>
       <c r="U37">
-        <v>9.01237315987298E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
+        <v>8.5756108838919605E-3</v>
+      </c>
+      <c r="V37">
+        <v>9.1938424777074906E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>3000</v>
       </c>
@@ -12771,52 +12883,55 @@
         <v>3.1469195501172501E-3</v>
       </c>
       <c r="G38">
-        <v>3.4122056066167999E-3</v>
+        <v>3.3328314055020101E-3</v>
       </c>
       <c r="H38">
-        <v>3.7250808794091999E-3</v>
+        <v>3.6590698491760802E-3</v>
       </c>
       <c r="I38">
-        <v>4.0916370637680399E-3</v>
+        <v>3.9060528291387999E-3</v>
       </c>
       <c r="J38">
-        <v>4.4514832288871696E-3</v>
+        <v>4.31584020946758E-3</v>
       </c>
       <c r="K38">
-        <v>4.77453002764736E-3</v>
+        <v>4.6339316176511203E-3</v>
       </c>
       <c r="L38">
-        <v>5.0363164768059999E-3</v>
+        <v>4.9242947239849701E-3</v>
       </c>
       <c r="M38">
-        <v>5.2668792640283204E-3</v>
+        <v>5.1668379652385302E-3</v>
       </c>
       <c r="N38">
-        <v>5.4619802916633297E-3</v>
+        <v>5.3836838063300498E-3</v>
       </c>
       <c r="O38">
-        <v>5.6427527657594402E-3</v>
+        <v>5.56392935825186E-3</v>
       </c>
       <c r="P38">
-        <v>5.8289472030873804E-3</v>
+        <v>5.7425060985755397E-3</v>
       </c>
       <c r="Q38">
-        <v>6.1263134364459198E-3</v>
+        <v>5.9261923680580496E-3</v>
       </c>
       <c r="R38">
-        <v>6.4930906739779004E-3</v>
+        <v>6.2880963354110799E-3</v>
       </c>
       <c r="S38">
-        <v>6.8536707096102101E-3</v>
+        <v>6.6387413261996802E-3</v>
       </c>
       <c r="T38">
-        <v>7.2150554371113798E-3</v>
+        <v>6.9953003415695403E-3</v>
       </c>
       <c r="U38">
-        <v>7.5766558283574597E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
+        <v>7.34536105146864E-3</v>
+      </c>
+      <c r="V38">
+        <v>7.6947468877524303E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>3200</v>
       </c>
@@ -12836,49 +12951,52 @@
         <v>2.5923270422694702E-3</v>
       </c>
       <c r="G39">
-        <v>2.7931911898271501E-3</v>
+        <v>2.73217237852334E-3</v>
       </c>
       <c r="H39">
-        <v>3.0314950756893302E-3</v>
+        <v>2.97477936792032E-3</v>
       </c>
       <c r="I39">
-        <v>3.3909618119616898E-3</v>
+        <v>3.18395458292569E-3</v>
       </c>
       <c r="J39">
-        <v>3.79285508263856E-3</v>
+        <v>3.6142548667002401E-3</v>
       </c>
       <c r="K39">
-        <v>4.1265192320570398E-3</v>
+        <v>3.9725278978169701E-3</v>
       </c>
       <c r="L39">
-        <v>4.4101168845079204E-3</v>
+        <v>4.2810739200041404E-3</v>
       </c>
       <c r="M39">
-        <v>4.6495234192237504E-3</v>
+        <v>4.5396928761573703E-3</v>
       </c>
       <c r="N39">
-        <v>4.8729783383058096E-3</v>
+        <v>4.7802979749314196E-3</v>
       </c>
       <c r="O39">
-        <v>5.06482222712975E-3</v>
+        <v>4.9810865762967499E-3</v>
       </c>
       <c r="P39">
-        <v>5.24561134710073E-3</v>
+        <v>5.1667339282071602E-3</v>
       </c>
       <c r="Q39">
-        <v>5.5519288909494698E-3</v>
+        <v>5.36019544595612E-3</v>
       </c>
       <c r="R39">
-        <v>5.93484337556214E-3</v>
+        <v>5.7316973922301997E-3</v>
       </c>
       <c r="S39">
-        <v>6.3282766470831699E-3</v>
+        <v>6.1312449371934297E-3</v>
       </c>
       <c r="T39">
-        <v>6.71496598837473E-3</v>
+        <v>6.5228885300049897E-3</v>
       </c>
       <c r="U39">
-        <v>7.0556252079185802E-3</v>
+        <v>6.87287151230435E-3</v>
+      </c>
+      <c r="V39">
+        <v>7.16511775341725E-3</v>
       </c>
     </row>
   </sheetData>
@@ -13124,7 +13242,7 @@
         <v>31</v>
       </c>
       <c r="F1" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s">
         <v>32</v>
@@ -15482,6 +15600,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA0FF96-1BF6-FB43-B297-6D0277385DE7}">
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
